--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486311_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486311_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3286</v>
+        <v>6.5443</v>
       </c>
       <c r="E2" t="n">
         <v>4.8954</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4331</v>
+        <v>1.6489</v>
       </c>
       <c r="G2" t="n">
         <v>5.8422</v>
@@ -610,13 +610,13 @@
         <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4863</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>0.0601</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4262</v>
+        <v>0.642</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. VAN ZEGEREN</t>
+          <t>C. ROGERS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.547</v>
+        <v>5.5694</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7607</v>
+        <v>4.958</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7862</v>
+        <v>0.6115</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5704</v>
+        <v>4.4215</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0717</v>
+        <v>1.168</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.5013</v>
+        <v>3.2536</v>
       </c>
       <c r="J3" t="n">
-        <v>1.647</v>
+        <v>5.9301</v>
       </c>
       <c r="K3" t="n">
-        <v>1.494</v>
+        <v>1.3203</v>
       </c>
       <c r="L3" t="n">
-        <v>0.153</v>
+        <v>4.6098</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0767</v>
+        <v>-1.5086</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5776</v>
+        <v>-0.1523</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6543</v>
+        <v>-1.3563</v>
       </c>
       <c r="P3" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4116</v>
+        <v>1.3654</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1583</v>
+        <v>0.1154</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2534</v>
+        <v>1.2501</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PERIS CRESPO</t>
+          <t>J. VAN ZEGEREN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8863</v>
+        <v>3.8544</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6003</v>
+        <v>3.3764</v>
       </c>
       <c r="F4" t="n">
-        <v>0.286</v>
+        <v>0.478</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5356</v>
+        <v>0.5704</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2599</v>
+        <v>2.0717</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2757</v>
+        <v>-1.5013</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1573</v>
+        <v>1.647</v>
       </c>
       <c r="K4" t="n">
-        <v>2.0138</v>
+        <v>1.494</v>
       </c>
       <c r="L4" t="n">
-        <v>2.1436</v>
+        <v>0.153</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6217</v>
+        <v>-1.0767</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2461</v>
+        <v>0.5776</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.8679</v>
+        <v>-1.6543</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7432</v>
+        <v>1.719</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0769</v>
+        <v>0.7739</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>1.695</v>
+        <v>1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>1.695</v>
+        <v>0.9554</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. ROGERS</t>
+          <t>J. PERIS CRESPO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7862</v>
+        <v>3.8007</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8837</v>
+        <v>3.6688</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0975</v>
+        <v>0.1318</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4215</v>
+        <v>2.5356</v>
       </c>
       <c r="H5" t="n">
-        <v>1.168</v>
+        <v>2.2599</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2536</v>
+        <v>0.2757</v>
       </c>
       <c r="J5" t="n">
-        <v>5.9301</v>
+        <v>4.1573</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3203</v>
+        <v>2.0138</v>
       </c>
       <c r="L5" t="n">
-        <v>4.6098</v>
+        <v>2.1436</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5086</v>
+        <v>-1.6217</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1523</v>
+        <v>0.2461</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3563</v>
+        <v>-1.8679</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4178</v>
+        <v>0.6576</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9589</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5411</v>
+        <v>0.666</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7205</v>
+        <v>3.1629</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4816</v>
+        <v>1.1089</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2389</v>
+        <v>2.054</v>
       </c>
       <c r="G6" t="n">
         <v>1.445</v>
@@ -922,13 +922,13 @@
         <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1149</v>
+        <v>0.3275</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9589</v>
+        <v>-0.3317</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8441</v>
+        <v>0.6591</v>
       </c>
       <c r="V6" t="n">
         <v>0.9554</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MARTINEZ CLARIANA</t>
+          <t>T. NASPLER PERAIRE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4903</v>
+        <v>2.2686</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1703</v>
+        <v>0.3216</v>
       </c>
       <c r="F7" t="n">
-        <v>2.32</v>
+        <v>1.9469</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0289</v>
+        <v>1.1387</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4743</v>
+        <v>0.5626</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4454</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4478</v>
+        <v>1.5173</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3555</v>
+        <v>0.3499</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8032</v>
+        <v>1.1674</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4767</v>
+        <v>-0.3786</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1188</v>
+        <v>0.2127</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3578</v>
+        <v>-0.5913</v>
       </c>
       <c r="P7" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4539</v>
+        <v>0.9124</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1454</v>
+        <v>-0.1081</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5993</v>
+        <v>1.0205</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>A. MARTINEZ CLARIANA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0552</v>
+        <v>2.0394</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8748</v>
+        <v>0.0585</v>
       </c>
       <c r="F8" t="n">
-        <v>3.93</v>
+        <v>1.9809</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.7041</v>
+        <v>-0.0289</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.8555</v>
+        <v>-0.4743</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1514</v>
+        <v>0.4454</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.7279</v>
+        <v>0.4478</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.9191</v>
+        <v>-0.3555</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1912</v>
+        <v>0.8032</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0238</v>
+        <v>-0.4767</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0636</v>
+        <v>-0.1188</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0399</v>
+        <v>-0.3578</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S8" t="n">
-        <v>3.7164</v>
+        <v>1.0031</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5502</v>
+        <v>-0.2572</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1662</v>
+        <v>1.2603</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3904</v>
+        <v>0.1952</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3904</v>
+        <v>0.9554</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. NASPLER PERAIRE</t>
+          <t>R. HERNANDEZ GALLARDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1472</v>
+        <v>1.0581</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4607</v>
+        <v>0.8577</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6079</v>
+        <v>0.2004</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1387</v>
+        <v>1.0067</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5626</v>
+        <v>1.0067</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5760999999999999</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5173</v>
+        <v>0.8577</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3499</v>
+        <v>0.8577</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1674</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3786</v>
+        <v>0.149</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2127</v>
+        <v>0.149</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5913</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.209</v>
+        <v>0.0514</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8904</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6815</v>
+        <v>0.0514</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. HERNANDEZ GALLARDO</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0273</v>
+        <v>0.0861</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8577</v>
+        <v>-3.1041</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1696</v>
+        <v>3.1902</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0067</v>
+        <v>-2.7041</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0067</v>
+        <v>-2.8555</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.1514</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8577</v>
+        <v>-2.7279</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8577</v>
+        <v>-2.9191</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.1912</v>
       </c>
       <c r="M10" t="n">
-        <v>0.149</v>
+        <v>0.0238</v>
       </c>
       <c r="N10" t="n">
-        <v>0.149</v>
+        <v>0.0636</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.0399</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0205</v>
+        <v>1.7473</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.3209</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0205</v>
+        <v>1.4264</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3032</v>
+        <v>-2.2733</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.849</v>
+        <v>-1.0041</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4542</v>
+        <v>-1.2693</v>
       </c>
       <c r="G11" t="n">
         <v>0.4637</v>
@@ -1312,13 +1312,13 @@
         <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5583</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1971</v>
+        <v>0.0421</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3612</v>
+        <v>0.5462</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4552</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6742</v>
+        <v>-2.7571</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7559</v>
+        <v>-3.0853</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.3283</v>
       </c>
       <c r="G12" t="n">
         <v>0.287</v>
@@ -1390,13 +1390,13 @@
         <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3014</v>
+        <v>1.2185</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6165</v>
+        <v>0.0541</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9177999999999999</v>
+        <v>1.1644</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5649999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>23.0112</v>
+        <v>23.3535</v>
       </c>
       <c r="E13" t="n">
-        <v>11.7093</v>
+        <v>12.0518</v>
       </c>
       <c r="F13" t="n">
-        <v>11.3017</v>
+        <v>11.3016</v>
       </c>
       <c r="G13" t="n">
         <v>14.9778</v>
@@ -1444,19 +1444,19 @@
         <v>20.5769</v>
       </c>
       <c r="K13" t="n">
-        <v>7.0901</v>
+        <v>7.090100000000001</v>
       </c>
       <c r="L13" t="n">
         <v>13.4867</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.5993</v>
+        <v>-5.599299999999999</v>
       </c>
       <c r="N13" t="n">
         <v>2.1266</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.7259</v>
+        <v>-7.725899999999999</v>
       </c>
       <c r="P13" t="n">
         <v>-3.2626</v>
@@ -1468,19 +1468,19 @@
         <v>10.8752</v>
       </c>
       <c r="S13" t="n">
-        <v>9.949900000000001</v>
+        <v>10.2925</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3186999999999998</v>
+        <v>0.6611000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>9.631400000000001</v>
+        <v>9.631500000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>1.345800000000001</v>
+        <v>1.3458</v>
       </c>
       <c r="W13" t="n">
-        <v>4.951600000000001</v>
+        <v>4.9516</v>
       </c>
       <c r="X13" t="n">
         <v>-3.6059</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.612</v>
+        <v>2.8971</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3126</v>
+        <v>2.5361</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2993</v>
+        <v>0.361</v>
       </c>
       <c r="G14" t="n">
         <v>2.9868</v>
@@ -1546,13 +1546,13 @@
         <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3324</v>
+        <v>-1.0473</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1644</v>
+        <v>-0.9409</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.168</v>
+        <v>-0.1064</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5649999999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. COMENDADOR FEMENIAS</t>
+          <t>A. SCARIOLO ARES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3829</v>
+        <v>0.9349</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9748</v>
+        <v>1.8287</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5919</v>
+        <v>-0.8938</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8331</v>
+        <v>1.1605</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3535</v>
+        <v>-0.0213</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.1866</v>
+        <v>1.1817</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6271</v>
+        <v>1.9104</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8167</v>
+        <v>0.1127</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1896</v>
+        <v>1.7977</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.4602</v>
+        <v>-0.7499</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4633</v>
+        <v>-0.1339</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.9969</v>
+        <v>-0.616</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R15" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2813</v>
+        <v>-0.0081</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5228</v>
+        <v>0.1358</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7585</v>
+        <v>-0.1439</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9347</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SCARIOLO ARES</t>
+          <t>A. COMENDADOR FEMENIAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1777</v>
+        <v>-0.093</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1639</v>
+        <v>1.7455</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9863</v>
+        <v>-1.8385</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1605</v>
+        <v>-0.8331</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0213</v>
+        <v>1.3535</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1817</v>
+        <v>-2.1866</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9104</v>
+        <v>2.6271</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1127</v>
+        <v>2.8167</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7977</v>
+        <v>-0.1896</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7499</v>
+        <v>-3.4602</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1339</v>
+        <v>-1.4633</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.616</v>
+        <v>-1.9969</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2347</v>
+        <v>-0.1947</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4711</v>
+        <v>-0.7066</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2364</v>
+        <v>0.5119</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.9347</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0092</v>
+        <v>-0.5507</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3995</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6097</v>
+        <v>-0.4864</v>
       </c>
       <c r="G17" t="n">
         <v>-1.0006</v>
@@ -1780,13 +1780,13 @@
         <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8563</v>
+        <v>-0.3978</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.411</v>
+        <v>-0.0757</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4454</v>
+        <v>-0.3221</v>
       </c>
       <c r="V17" t="n">
         <v>0.1952</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8529</v>
+        <v>-2.111</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6348</v>
+        <v>-0.523</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2181</v>
+        <v>-1.588</v>
       </c>
       <c r="G18" t="n">
         <v>-1.2141</v>
@@ -1858,13 +1858,13 @@
         <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9231</v>
+        <v>-1.1813</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3014</v>
+        <v>-1.1897</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3783</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5857</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. DIKE EGUN</t>
+          <t>T. HOLLOWELL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.9728</v>
+        <v>-2.5827</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3066</v>
+        <v>-0.1854</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6662</v>
+        <v>-2.3974</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4819</v>
+        <v>-2.4638</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4357</v>
+        <v>-2.1595</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0462</v>
+        <v>-0.3044</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0481</v>
+        <v>1.1614</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8514</v>
+        <v>0.2983</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8032</v>
+        <v>0.863</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4337</v>
+        <v>-3.6252</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5843</v>
+        <v>-2.4578</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8495</v>
+        <v>-1.1674</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.144</v>
+        <v>-1.2489</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3014</v>
+        <v>-1.1716</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1574</v>
+        <v>-0.0772</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8695</v>
+        <v>1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7395</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. HOLLOWELL</t>
+          <t>G. DIKE EGUN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0721</v>
+        <v>-2.7493</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5206</v>
+        <v>-2.0831</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5515</v>
+        <v>-0.6662</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4638</v>
+        <v>-1.4819</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1595</v>
+        <v>-1.4357</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3044</v>
+        <v>-0.0462</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1614</v>
+        <v>-0.0481</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2983</v>
+        <v>-0.8514</v>
       </c>
       <c r="L20" t="n">
-        <v>0.863</v>
+        <v>0.8032</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.6252</v>
+        <v>-1.4337</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.4578</v>
+        <v>-0.5843</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1674</v>
+        <v>-0.8495</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.5225</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7382</v>
+        <v>-0.9205</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.5069</v>
+        <v>-1.0779</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2313</v>
+        <v>0.1574</v>
       </c>
       <c r="V20" t="n">
-        <v>1.13</v>
+        <v>-1.8695</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>-0.7395</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>H. ATENCIA SUAREZ</t>
+          <t>I. MASSOUD RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8884</v>
+        <v>-3.6968</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5575</v>
+        <v>-3.801</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3309</v>
+        <v>0.1043</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7049</v>
+        <v>-3.9579</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8643</v>
+        <v>-1.1713</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8406</v>
+        <v>-2.7866</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1563</v>
+        <v>-1.1733</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0791</v>
+        <v>-0.4681</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9228</v>
+        <v>-0.7052</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5486</v>
+        <v>-2.7845</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7852</v>
+        <v>-0.7030999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7635</v>
+        <v>-2.0814</v>
       </c>
       <c r="P21" t="n">
-        <v>-0</v>
+        <v>0.435</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1751</v>
+        <v>2.6101</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9437</v>
+        <v>-1.6737</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.9864</v>
+        <v>-1.5826</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0427</v>
+        <v>-0.091</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7602</v>
+        <v>1.4997</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7602</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. MASSOUD RODRÍGUEZ</t>
+          <t>H. ATENCIA SUAREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1245</v>
+        <v>-3.7343</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1363</v>
+        <v>-3.5575</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0118</v>
+        <v>-0.1768</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.9579</v>
+        <v>-2.7049</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1713</v>
+        <v>-1.8643</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.7866</v>
+        <v>-0.8406</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1733</v>
+        <v>-0.1563</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4681</v>
+        <v>-1.0791</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7052</v>
+        <v>0.9228</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7845</v>
+        <v>-2.5486</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7030999999999999</v>
+        <v>-0.7852</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.0814</v>
+        <v>-1.7635</v>
       </c>
       <c r="P22" t="n">
-        <v>0.435</v>
+        <v>-0</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>2.6101</v>
+        <v>2.1751</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.1014</v>
+        <v>-1.7896</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.9179</v>
+        <v>-1.9864</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1835</v>
+        <v>0.1968</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4997</v>
+        <v>0.7602</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>0.7602</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1923</v>
+        <v>-3.8069</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5057</v>
+        <v>-2.0587</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6866</v>
+        <v>-1.7482</v>
       </c>
       <c r="G23" t="n">
         <v>-0.4969</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7177</v>
+        <v>-0.3323</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.2379</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0327</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8902</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.0713</v>
+        <v>-7.5183</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.692</v>
+        <v>-5.1391</v>
       </c>
       <c r="F24" t="n">
         <v>-2.3792</v>
@@ -2326,10 +2326,10 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.709</v>
+        <v>-1.156</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3509</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="U24" t="n">
         <v>-0.3581</v>
@@ -2359,43 +2359,43 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-23.0109</v>
+        <v>-23.011</v>
       </c>
       <c r="E25" t="n">
         <v>-11.3017</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.7093</v>
+        <v>-11.7092</v>
       </c>
       <c r="G25" t="n">
         <v>-14.9777</v>
       </c>
       <c r="H25" t="n">
-        <v>-9.216699999999999</v>
+        <v>-9.216700000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-5.761100000000001</v>
+        <v>-5.761099999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>5.599500000000001</v>
+        <v>5.599499999999999</v>
       </c>
       <c r="K25" t="n">
         <v>-2.1265</v>
       </c>
       <c r="L25" t="n">
-        <v>7.725900000000001</v>
+        <v>7.725900000000003</v>
       </c>
       <c r="M25" t="n">
         <v>-20.577</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.090100000000001</v>
+        <v>-7.0901</v>
       </c>
       <c r="O25" t="n">
         <v>-13.4871</v>
       </c>
       <c r="P25" t="n">
-        <v>3.262499999999999</v>
+        <v>3.2625</v>
       </c>
       <c r="Q25" t="n">
         <v>-10.8753</v>
@@ -2404,7 +2404,7 @@
         <v>14.1378</v>
       </c>
       <c r="S25" t="n">
-        <v>-9.9498</v>
+        <v>-9.950200000000001</v>
       </c>
       <c r="T25" t="n">
         <v>-9.631399999999999</v>
@@ -2419,7 +2419,7 @@
         <v>3.6059</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.951700000000001</v>
+        <v>-4.9517</v>
       </c>
     </row>
   </sheetData>
